--- a/xk/output/Q4_result_filled.xlsx
+++ b/xk/output/Q4_result_filled.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>460.7</v>
+        <v>459</v>
       </c>
       <c r="E7" t="n">
-        <v>462.2</v>
+        <v>460.5</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>463.2</v>
+        <v>461.7</v>
       </c>
       <c r="E8" t="n">
-        <v>463.7</v>
+        <v>462.2</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>466.8</v>
+        <v>463.2</v>
       </c>
       <c r="E9" t="n">
-        <v>467.3</v>
+        <v>463.7</v>
       </c>
     </row>
     <row r="10">
@@ -700,19 +700,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>468.1</v>
+        <v>464.9</v>
       </c>
       <c r="E10" t="n">
-        <v>469.6</v>
+        <v>465.4</v>
       </c>
     </row>
     <row r="11">
@@ -721,19 +721,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>477</v>
+        <v>466.8</v>
       </c>
       <c r="E11" t="n">
-        <v>478.5</v>
+        <v>467.3</v>
       </c>
     </row>
     <row r="12">
@@ -742,19 +742,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>479.4</v>
+        <v>467.8</v>
       </c>
       <c r="E12" t="n">
-        <v>479.9</v>
+        <v>469.3</v>
       </c>
     </row>
     <row r="13">
@@ -763,19 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>480.6</v>
+        <v>477.3</v>
       </c>
       <c r="E13" t="n">
-        <v>481.1</v>
+        <v>478.8</v>
       </c>
     </row>
     <row r="14">
@@ -784,19 +784,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>492.9</v>
+        <v>479.1</v>
       </c>
       <c r="E14" t="n">
-        <v>493.4</v>
+        <v>480.6</v>
       </c>
     </row>
     <row r="15">
@@ -805,19 +805,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>494.3</v>
+        <v>480.7</v>
       </c>
       <c r="E15" t="n">
-        <v>494.8</v>
+        <v>482.2</v>
       </c>
     </row>
     <row r="16">
@@ -826,7 +826,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>507.8</v>
+        <v>493.2</v>
       </c>
       <c r="E16" t="n">
-        <v>508.3</v>
+        <v>493.7</v>
       </c>
     </row>
     <row r="17">
@@ -847,19 +847,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>511.2</v>
+        <v>493.8</v>
       </c>
       <c r="E17" t="n">
-        <v>512.7</v>
+        <v>494.3</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>516.7</v>
+        <v>508.1</v>
       </c>
       <c r="E18" t="n">
-        <v>518.2</v>
+        <v>508.6</v>
       </c>
     </row>
     <row r="19">
@@ -889,7 +889,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>650.3</v>
+        <v>511.2</v>
       </c>
       <c r="E19" t="n">
-        <v>651.8</v>
+        <v>512.7</v>
       </c>
     </row>
     <row r="20">
@@ -910,7 +910,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>750.1</v>
+        <v>516.7</v>
       </c>
       <c r="E20" t="n">
-        <v>751.6</v>
+        <v>518.2</v>
       </c>
     </row>
     <row r="21">
@@ -931,7 +931,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -940,13 +940,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>762.3</v>
+        <v>749.2</v>
       </c>
       <c r="E21" t="n">
-        <v>763.8</v>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>750.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>766.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>767.7</v>
+      </c>
+    </row>
+    <row r="23"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/xk/output/Q4_result_filled.xlsx
+++ b/xk/output/Q4_result_filled.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>449.9</v>
+        <v>446.1</v>
       </c>
       <c r="E3" t="n">
-        <v>450.4</v>
+        <v>446.6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -550,19 +550,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>450.7</v>
+        <v>448.2</v>
       </c>
       <c r="E4" t="n">
-        <v>451.2</v>
+        <v>449.7</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -590,19 +590,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>452.1</v>
+        <v>449.8</v>
       </c>
       <c r="E5" t="n">
-        <v>452.6</v>
+        <v>451.3</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -616,19 +616,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>453.9</v>
+        <v>451.4</v>
       </c>
       <c r="E6" t="n">
-        <v>454.4</v>
+        <v>452.9</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +637,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E7" t="n">
-        <v>460.5</v>
+        <v>454.5</v>
       </c>
     </row>
     <row r="8">
@@ -658,19 +658,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>461.7</v>
+        <v>454.6</v>
       </c>
       <c r="E8" t="n">
-        <v>462.2</v>
+        <v>456.1</v>
       </c>
     </row>
     <row r="9">
@@ -679,19 +679,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>463.2</v>
+        <v>456.2</v>
       </c>
       <c r="E9" t="n">
-        <v>463.7</v>
+        <v>457.7</v>
       </c>
     </row>
     <row r="10">
@@ -700,19 +700,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>464.9</v>
+        <v>457.8</v>
       </c>
       <c r="E10" t="n">
-        <v>465.4</v>
+        <v>459.3</v>
       </c>
     </row>
     <row r="11">
@@ -721,19 +721,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>466.8</v>
+        <v>459.4</v>
       </c>
       <c r="E11" t="n">
-        <v>467.3</v>
+        <v>460.9</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>467.8</v>
+        <v>461</v>
       </c>
       <c r="E12" t="n">
-        <v>469.3</v>
+        <v>462.5</v>
       </c>
     </row>
     <row r="13">
@@ -763,7 +763,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>477.3</v>
+        <v>462.6</v>
       </c>
       <c r="E13" t="n">
-        <v>478.8</v>
+        <v>464.1</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>479.1</v>
+        <v>464.2</v>
       </c>
       <c r="E14" t="n">
-        <v>480.6</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="15">
@@ -805,7 +805,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>480.7</v>
+        <v>465.8</v>
       </c>
       <c r="E15" t="n">
-        <v>482.2</v>
+        <v>467.3</v>
       </c>
     </row>
     <row r="16">
@@ -826,19 +826,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>493.2</v>
+        <v>467.4</v>
       </c>
       <c r="E16" t="n">
-        <v>493.7</v>
+        <v>468.9</v>
       </c>
     </row>
     <row r="17">
@@ -847,19 +847,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>493.8</v>
+        <v>477.3</v>
       </c>
       <c r="E17" t="n">
-        <v>494.3</v>
+        <v>478.8</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>508.1</v>
+        <v>478.9</v>
       </c>
       <c r="E18" t="n">
-        <v>508.6</v>
+        <v>480.4</v>
       </c>
     </row>
     <row r="19">
@@ -889,7 +889,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>511.2</v>
+        <v>480.5</v>
       </c>
       <c r="E19" t="n">
-        <v>512.7</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20">
@@ -910,7 +910,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>516.7</v>
+        <v>492</v>
       </c>
       <c r="E20" t="n">
-        <v>518.2</v>
+        <v>493.5</v>
       </c>
     </row>
     <row r="21">
@@ -931,7 +931,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>749.2</v>
+        <v>493.6</v>
       </c>
       <c r="E21" t="n">
-        <v>750.7</v>
+        <v>495.1</v>
       </c>
     </row>
     <row r="22">
@@ -952,22 +952,253 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>拍照</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>508.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>516.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>517.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>518</v>
+      </c>
+      <c r="E24" t="n">
+        <v>519.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>766.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>767.7</v>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>521.2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>522.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>526</v>
+      </c>
+      <c r="E26" t="n">
+        <v>527.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>532.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>533.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>534</v>
+      </c>
+      <c r="E28" t="n">
+        <v>535.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>535.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>537.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>749.2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>750.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>750.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>752.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>771</v>
+      </c>
+      <c r="E32" t="n">
+        <v>772.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>811</v>
+      </c>
+      <c r="E33" t="n">
+        <v>812.5</v>
+      </c>
+    </row>
+    <row r="34"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/xk/output/Q4_result_filled.xlsx
+++ b/xk/output/Q4_result_filled.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -504,19 +504,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>446.1</v>
+        <v>446.5</v>
       </c>
       <c r="E3" t="n">
-        <v>446.6</v>
+        <v>448</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>448.2</v>
+        <v>448</v>
       </c>
       <c r="E4" t="n">
-        <v>449.7</v>
+        <v>449.5</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -590,7 +590,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>449.8</v>
+        <v>449.5</v>
       </c>
       <c r="E5" t="n">
-        <v>451.3</v>
+        <v>451</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>451.4</v>
+        <v>451</v>
       </c>
       <c r="E6" t="n">
-        <v>452.9</v>
+        <v>452.5</v>
       </c>
     </row>
     <row r="7">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>453</v>
+        <v>452.5</v>
       </c>
       <c r="E7" t="n">
-        <v>454.5</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>454.6</v>
+        <v>454</v>
       </c>
       <c r="E8" t="n">
-        <v>456.1</v>
+        <v>455.5</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>456.2</v>
+        <v>455.5</v>
       </c>
       <c r="E9" t="n">
-        <v>457.7</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10">
@@ -700,7 +700,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>457.8</v>
+        <v>457</v>
       </c>
       <c r="E10" t="n">
-        <v>459.3</v>
+        <v>458.5</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>459.4</v>
+        <v>458.5</v>
       </c>
       <c r="E11" t="n">
-        <v>460.9</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E12" t="n">
-        <v>462.5</v>
+        <v>461.5</v>
       </c>
     </row>
     <row r="13">
@@ -763,7 +763,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>462.6</v>
+        <v>461.5</v>
       </c>
       <c r="E13" t="n">
-        <v>464.1</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>464.2</v>
+        <v>463</v>
       </c>
       <c r="E14" t="n">
-        <v>465.7</v>
+        <v>464.5</v>
       </c>
     </row>
     <row r="15">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>465.8</v>
+        <v>464.5</v>
       </c>
       <c r="E15" t="n">
-        <v>467.3</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16">
@@ -826,7 +826,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>467.4</v>
+        <v>466</v>
       </c>
       <c r="E16" t="n">
-        <v>468.9</v>
+        <v>467.5</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>477.3</v>
+        <v>468.1</v>
       </c>
       <c r="E17" t="n">
-        <v>478.8</v>
+        <v>469.6</v>
       </c>
     </row>
     <row r="18">
@@ -868,7 +868,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>478.9</v>
+        <v>477</v>
       </c>
       <c r="E18" t="n">
-        <v>480.4</v>
+        <v>478.5</v>
       </c>
     </row>
     <row r="19">
@@ -889,19 +889,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>480.5</v>
+        <v>479.4</v>
       </c>
       <c r="E19" t="n">
-        <v>482</v>
+        <v>479.9</v>
       </c>
     </row>
     <row r="20">
@@ -910,19 +910,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>492</v>
+        <v>479.9</v>
       </c>
       <c r="E20" t="n">
-        <v>493.5</v>
+        <v>480.4</v>
       </c>
     </row>
     <row r="21">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>493.6</v>
+        <v>491.8</v>
       </c>
       <c r="E21" t="n">
-        <v>495.1</v>
+        <v>493.3</v>
       </c>
     </row>
     <row r="22">
@@ -952,19 +952,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>508.1</v>
+        <v>493.3</v>
       </c>
       <c r="E22" t="n">
-        <v>508.6</v>
+        <v>494.8</v>
       </c>
     </row>
     <row r="23">
@@ -973,19 +973,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>516.4</v>
+        <v>507.8</v>
       </c>
       <c r="E23" t="n">
-        <v>517.9</v>
+        <v>508.3</v>
       </c>
     </row>
     <row r="24">
@@ -994,7 +994,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>518</v>
+        <v>509.4</v>
       </c>
       <c r="E24" t="n">
-        <v>519.5</v>
+        <v>510.9</v>
       </c>
     </row>
     <row r="25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>521.2</v>
+        <v>513.9</v>
       </c>
       <c r="E25" t="n">
-        <v>522.7</v>
+        <v>515.4</v>
       </c>
     </row>
     <row r="26">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>526</v>
+        <v>516.9</v>
       </c>
       <c r="E26" t="n">
-        <v>527.5</v>
+        <v>518.4</v>
       </c>
     </row>
     <row r="27">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>532.4</v>
+        <v>533.4</v>
       </c>
       <c r="E27" t="n">
-        <v>533.9</v>
+        <v>534.9</v>
       </c>
     </row>
     <row r="28">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>534</v>
+        <v>534.9</v>
       </c>
       <c r="E28" t="n">
-        <v>535.5</v>
+        <v>536.4</v>
       </c>
     </row>
     <row r="29">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>535.6</v>
+        <v>536.4</v>
       </c>
       <c r="E29" t="n">
-        <v>537.1</v>
+        <v>537.9</v>
       </c>
     </row>
     <row r="30">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>749.2</v>
+        <v>748.8</v>
       </c>
       <c r="E30" t="n">
-        <v>750.7</v>
+        <v>750.3</v>
       </c>
     </row>
     <row r="31">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>750.8</v>
+        <v>750.3</v>
       </c>
       <c r="E31" t="n">
-        <v>752.3</v>
+        <v>751.8</v>
       </c>
     </row>
     <row r="32">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>771</v>
+        <v>751.8</v>
       </c>
       <c r="E32" t="n">
-        <v>772.5</v>
+        <v>753.3</v>
       </c>
     </row>
     <row r="33">
@@ -1183,22 +1183,85 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>762.3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>763.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>811</v>
-      </c>
-      <c r="E33" t="n">
-        <v>812.5</v>
-      </c>
-    </row>
-    <row r="34"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>769.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>771.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>789.3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>790.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>射击</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>793.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>795.3</v>
+      </c>
+    </row>
+    <row r="37"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/xk/output/Q4_result_filled.xlsx
+++ b/xk/output/Q4_result_filled.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S08</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>466</v>
+        <v>466.5</v>
       </c>
       <c r="E16" t="n">
-        <v>467.5</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17">
@@ -868,7 +868,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -931,19 +931,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>491.8</v>
+        <v>492.9</v>
       </c>
       <c r="E21" t="n">
-        <v>493.3</v>
+        <v>493.4</v>
       </c>
     </row>
     <row r="22">
@@ -952,19 +952,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>493.3</v>
+        <v>507.8</v>
       </c>
       <c r="E22" t="n">
-        <v>494.8</v>
+        <v>508.3</v>
       </c>
     </row>
     <row r="23">
@@ -973,19 +973,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>507.8</v>
+        <v>533.4</v>
       </c>
       <c r="E23" t="n">
-        <v>508.3</v>
+        <v>534.9</v>
       </c>
     </row>
     <row r="24">
@@ -994,7 +994,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>509.4</v>
+        <v>534.9</v>
       </c>
       <c r="E24" t="n">
-        <v>510.9</v>
+        <v>536.4</v>
       </c>
     </row>
     <row r="25">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>513.9</v>
+        <v>536.4</v>
       </c>
       <c r="E25" t="n">
-        <v>515.4</v>
+        <v>537.9</v>
       </c>
     </row>
     <row r="26">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>516.9</v>
+        <v>748.8</v>
       </c>
       <c r="E26" t="n">
-        <v>518.4</v>
+        <v>750.3</v>
       </c>
     </row>
     <row r="27">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>533.4</v>
+        <v>750.3</v>
       </c>
       <c r="E27" t="n">
-        <v>534.9</v>
+        <v>751.8</v>
       </c>
     </row>
     <row r="28">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>534.9</v>
+        <v>751.8</v>
       </c>
       <c r="E28" t="n">
-        <v>536.4</v>
+        <v>753.3</v>
       </c>
     </row>
     <row r="29">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>536.4</v>
+        <v>762.3</v>
       </c>
       <c r="E29" t="n">
-        <v>537.9</v>
+        <v>763.8</v>
       </c>
     </row>
     <row r="30">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>748.8</v>
+        <v>778.8</v>
       </c>
       <c r="E30" t="n">
-        <v>750.3</v>
+        <v>780.3</v>
       </c>
     </row>
     <row r="31">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>750.3</v>
+        <v>784.8</v>
       </c>
       <c r="E31" t="n">
-        <v>751.8</v>
+        <v>786.3</v>
       </c>
     </row>
     <row r="32">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>751.8</v>
+        <v>793.8</v>
       </c>
       <c r="E32" t="n">
-        <v>753.3</v>
+        <v>795.3</v>
       </c>
     </row>
     <row r="33">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>762.3</v>
+        <v>796.8</v>
       </c>
       <c r="E33" t="n">
-        <v>763.8</v>
+        <v>798.3</v>
       </c>
     </row>
     <row r="34">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>769.8</v>
+        <v>799.8</v>
       </c>
       <c r="E34" t="n">
-        <v>771.3</v>
+        <v>801.3</v>
       </c>
     </row>
     <row r="35">
@@ -1234,34 +1234,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>789.3</v>
+        <v>807.3</v>
       </c>
       <c r="E35" t="n">
-        <v>790.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>射击</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>793.8</v>
-      </c>
-      <c r="E36" t="n">
-        <v>795.3</v>
-      </c>
-    </row>
-    <row r="37"/>
+        <v>808.8</v>
+      </c>
+    </row>
+    <row r="36"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
